--- a/webcrawler/data/servents.xlsx
+++ b/webcrawler/data/servents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F478"/>
+  <dimension ref="A1:F486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12498,7 +12498,11 @@
           <t>圖坦卡蒙</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>圖坦卡門</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -12522,7 +12526,11 @@
           <t>梵高〔礦工〕</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>梵谷〔礦工〕</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -12546,7 +12554,11 @@
           <t>婁希</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>婁希</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -12570,7 +12582,11 @@
           <t>阿比蓋爾·威廉姆斯〔聖誕〕</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>艾比蓋兒．威廉斯〔Santa〕</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -12925,7 +12941,11 @@
           <t>パッションリップ</t>
         </is>
       </c>
-      <c r="E450" t="inlineStr"/>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Passionlip</t>
+        </is>
+      </c>
       <c r="F450" t="inlineStr"/>
     </row>
     <row r="451">
@@ -12945,7 +12965,11 @@
           <t>クリームヒルト</t>
         </is>
       </c>
-      <c r="E451" t="inlineStr"/>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>克里姆希爾德</t>
+        </is>
+      </c>
       <c r="F451" t="inlineStr"/>
     </row>
     <row r="452">
@@ -12965,7 +12989,11 @@
           <t>呼延灼</t>
         </is>
       </c>
-      <c r="E452" t="inlineStr"/>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>吾綽</t>
+        </is>
+      </c>
       <c r="F452" t="inlineStr"/>
     </row>
     <row r="453">
@@ -12985,7 +13013,11 @@
           <t>玉兎</t>
         </is>
       </c>
-      <c r="E453" t="inlineStr"/>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>玉兔</t>
+        </is>
+      </c>
       <c r="F453" t="inlineStr"/>
     </row>
     <row r="454">
@@ -13005,7 +13037,11 @@
           <t>美遊・エーデルフェルト</t>
         </is>
       </c>
-      <c r="E454" t="inlineStr"/>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>美遊·艾德費爾特</t>
+        </is>
+      </c>
       <c r="F454" t="inlineStr"/>
     </row>
     <row r="455">
@@ -13025,7 +13061,11 @@
           <t>ラーヴァ／ティアマト</t>
         </is>
       </c>
-      <c r="E455" t="inlineStr"/>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>幼體／提亞馬特</t>
+        </is>
+      </c>
       <c r="F455" t="inlineStr"/>
     </row>
     <row r="456">
@@ -13045,7 +13085,11 @@
           <t>ジュネス・クレーン</t>
         </is>
       </c>
-      <c r="E456" t="inlineStr"/>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>熱內斯·克萊恩</t>
+        </is>
+      </c>
       <c r="F456" t="inlineStr"/>
     </row>
     <row r="457">
@@ -13065,7 +13109,11 @@
           <t>ネモ／ノア</t>
         </is>
       </c>
-      <c r="E457" t="inlineStr"/>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>尼莫／諾亞</t>
+        </is>
+      </c>
       <c r="F457" t="inlineStr"/>
     </row>
     <row r="458">
@@ -13487,6 +13535,166 @@
       </c>
       <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>474</v>
+      </c>
+      <c r="B479" t="n">
+        <v>5</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Assassin</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>ハサン・サッバーハ</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>475</v>
+      </c>
+      <c r="B480" t="n">
+        <v>5</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Berserker</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>紅閻魔</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>476</v>
+      </c>
+      <c r="B481" t="n">
+        <v>5</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Mooncancer</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>キングプロテア</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>477</v>
+      </c>
+      <c r="B482" t="n">
+        <v>4</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Caster</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>ビショーネ</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>478</v>
+      </c>
+      <c r="B483" t="n">
+        <v>5</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Rider</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>リリス</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>479</v>
+      </c>
+      <c r="B484" t="n">
+        <v>5</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Avenger</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>キングプロテア・オルタ</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>480</v>
+      </c>
+      <c r="B485" t="n">
+        <v>4</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>小野小町</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>481</v>
+      </c>
+      <c r="B486" t="n">
+        <v>4</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Pretender</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>ハベトロット</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
